--- a/fixbugversion/ig/StructureDefinition-fr-lm-comparaison-examens-imagerie.xlsx
+++ b/fixbugversion/ig/StructureDefinition-fr-lm-comparaison-examens-imagerie.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapshot</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:14:55+00:00</t>
+    <t>2026-04-15T14:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
